--- a/results/ai_run/542_z06/5_quantification/542_z06_quantification.xlsx
+++ b/results/ai_run/542_z06/5_quantification/542_z06_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.2667</v>
+        <v>15.8</v>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>7.2749</v>
+        <v>7.1933</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.4008</v>
+        <v>5.7574</v>
       </c>
       <c r="D25" t="n">
-        <v>6.0551</v>
+        <v>5.5065</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1701</v>
+        <v>1.7381</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2913,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
         <v>324</v>
@@ -2952,7 +2952,7 @@
         <v>0.04732067</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.5649</v>
+        <v>7.9061</v>
       </c>
       <c r="Z5" t="n">
         <v>320</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
         <v>519</v>
@@ -3059,7 +3059,7 @@
         <v>0.04099704</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.0367</v>
+        <v>3.1052</v>
       </c>
       <c r="Z6" t="n">
         <v>468</v>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M8" t="n">
         <v>424</v>
@@ -3273,7 +3273,7 @@
         <v>0.04048604</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.493600000000001</v>
+        <v>8.021699999999999</v>
       </c>
       <c r="Z8" t="n">
         <v>362</v>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M9" t="n">
         <v>480</v>
@@ -3380,7 +3380,7 @@
         <v>0.03349282</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.7329</v>
+        <v>4.4545</v>
       </c>
       <c r="Z9" t="n">
         <v>436</v>
@@ -3448,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
         <v>433</v>
@@ -3487,7 +3487,7 @@
         <v>0.04084763</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.9757</v>
+        <v>2.3144</v>
       </c>
       <c r="Z10" t="n">
         <v>378</v>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M11" t="n">
         <v>525</v>
@@ -3594,7 +3594,7 @@
         <v>0.04680761</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.1385</v>
+        <v>5.4923</v>
       </c>
       <c r="Z11" t="n">
         <v>525</v>
@@ -3662,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M12" t="n">
         <v>912</v>
@@ -3701,7 +3701,7 @@
         <v>0.05701549</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.9794</v>
+        <v>5.7659</v>
       </c>
       <c r="Z12" t="n">
         <v>843</v>
@@ -3769,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M13" t="n">
         <v>653</v>
@@ -3808,7 +3808,7 @@
         <v>0.04633179</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.9105</v>
+        <v>5.2012</v>
       </c>
       <c r="Z13" t="n">
         <v>611</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M14" t="n">
         <v>650</v>
@@ -3915,7 +3915,7 @@
         <v>0.04235704</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.0551</v>
+        <v>5.2653</v>
       </c>
       <c r="Z14" t="n">
         <v>617</v>
@@ -4090,7 +4090,7 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M16" t="n">
         <v>405</v>
@@ -4129,7 +4129,7 @@
         <v>0.03931782</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.3044</v>
+        <v>2.7036</v>
       </c>
       <c r="Z16" t="n">
         <v>389</v>
@@ -4197,7 +4197,7 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
         <v>240</v>
@@ -4236,7 +4236,7 @@
         <v>0.03637586</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.8877</v>
+        <v>2.9158</v>
       </c>
       <c r="Z17" t="n">
         <v>224</v>
@@ -4283,7 +4283,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M18" t="n">
         <v>699</v>
@@ -4322,7 +4322,7 @@
         <v>0.04624036</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.9286</v>
+        <v>5.1553</v>
       </c>
       <c r="Z18" t="n">
         <v>654</v>
@@ -4369,7 +4369,7 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
         <v>112</v>
@@ -4408,7 +4408,7 @@
         <v>0.02889171</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.5974</v>
+        <v>3.448</v>
       </c>
       <c r="Z19" t="n">
         <v>112</v>
@@ -4455,7 +4455,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M20" t="n">
         <v>168</v>
@@ -4494,7 +4494,7 @@
         <v>0.03525596</v>
       </c>
       <c r="Y20" t="n">
-        <v>12.3088</v>
+        <v>8.792</v>
       </c>
       <c r="Z20" t="n">
         <v>106</v>
